--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512449_1ºEA1ºEBFINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512449_1ºEA1ºEBFINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0772</v>
+        <v>3.0738</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2144</v>
+        <v>0.2569</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2916</v>
+        <v>2.8169</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0662</v>
+        <v>3.951</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2899</v>
+        <v>1.2233</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7764</v>
+        <v>2.7278</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5195</v>
+        <v>2.5679</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1197</v>
+        <v>1.1495</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3998</v>
+        <v>1.4184</v>
       </c>
       <c r="M2" t="n">
-        <v>1.5467</v>
+        <v>1.3831</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1702</v>
+        <v>0.0738</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3766</v>
+        <v>1.3093</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4007</v>
+        <v>-2.3368</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0506</v>
+        <v>0.1933</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3332</v>
+        <v>0.0259</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3839</v>
+        <v>0.1675</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.6811</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.6811</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7649</v>
+        <v>2.1316</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3692</v>
+        <v>0.9204</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3956</v>
+        <v>1.2112</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0824</v>
+        <v>-0.0716</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1379</v>
+        <v>-1.1366</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0555</v>
+        <v>1.065</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.4525</v>
+        <v>-0.3559</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4163</v>
+        <v>-0.3643</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0362</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3701</v>
+        <v>0.2843</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7216</v>
+        <v>-0.7723</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0917</v>
+        <v>1.0566</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.033</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4378</v>
+        <v>-0.0295</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5952</v>
+        <v>-0.6241</v>
       </c>
       <c r="V3" t="n">
-        <v>1.88</v>
+        <v>1.8832</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DE LA CAL DOMINGUEZ</t>
+          <t>J. RODENAS SANCHEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.613</v>
+        <v>1.5556</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5923</v>
+        <v>-1.5067</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2054</v>
+        <v>3.0623</v>
       </c>
       <c r="G4" t="n">
-        <v>2.291</v>
+        <v>3.6643</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1487</v>
+        <v>3.9122</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4397</v>
+        <v>-0.2479</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1269</v>
+        <v>1.8101</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6544</v>
+        <v>3.6332</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5275</v>
+        <v>-1.8231</v>
       </c>
       <c r="M4" t="n">
-        <v>2.4178</v>
+        <v>1.8542</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5057</v>
+        <v>0.279</v>
       </c>
       <c r="O4" t="n">
-        <v>1.9121</v>
+        <v>1.5751</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8002</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2006</v>
+        <v>-4.0895</v>
       </c>
       <c r="R4" t="n">
-        <v>3.0009</v>
+        <v>2.3368</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.678</v>
+        <v>-0.8445</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0158</v>
+        <v>-0.3968</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6938</v>
+        <v>-0.4476</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.8002</v>
+        <v>0.4884</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7194</v>
+        <v>1.1695</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.5195</v>
+        <v>-0.6811</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. RODENAS SANCHEZ</t>
+          <t>A. DE LA CAL DOMINGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5762</v>
+        <v>1.5476</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.6643</v>
+        <v>-0.3553</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2404</v>
+        <v>1.9028</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6467</v>
+        <v>2.3069</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9091</v>
+        <v>-0.1653</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2624</v>
+        <v>2.4721</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6288</v>
+        <v>0.0474</v>
       </c>
       <c r="K5" t="n">
-        <v>3.539</v>
+        <v>-0.5772</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.9102</v>
+        <v>0.6246</v>
       </c>
       <c r="M5" t="n">
-        <v>2.0179</v>
+        <v>2.2594</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3701</v>
+        <v>0.4119</v>
       </c>
       <c r="O5" t="n">
-        <v>1.6478</v>
+        <v>1.8475</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.8005</v>
+        <v>0.7789</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.2012</v>
+        <v>-2.1421</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4007</v>
+        <v>2.921</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.7499</v>
+        <v>-0.754</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2113</v>
+        <v>-0.0406</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5386</v>
+        <v>-0.7134</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4799</v>
+        <v>-0.7842</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1195</v>
+        <v>1.78</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-2.5642</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. MASIP CANTERO</t>
+          <t>H. GOMEZ GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4626</v>
+        <v>0.7912</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.552</v>
+        <v>0.64</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0146</v>
+        <v>0.1512</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1533</v>
+        <v>0.2335</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0786</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2319</v>
+        <v>0.739</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1492</v>
+        <v>0.1426</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1706</v>
+        <v>0.0616</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3198</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>2.0041</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>0.092</v>
+        <v>-0.5671</v>
       </c>
       <c r="O6" t="n">
-        <v>1.9121</v>
+        <v>0.6579</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6002</v>
+        <v>0.1947</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2006</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6005</v>
+        <v>1.1684</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9298999999999999</v>
+        <v>0.2056</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0602</v>
+        <v>-0.0295</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.99</v>
+        <v>0.2351</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1606</v>
+        <v>0.1574</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4393</v>
+        <v>1.5005</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5999</v>
+        <v>-1.3432</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. YURCHENKO</t>
+          <t>D. MASIP CANTERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0774</v>
+        <v>0.6425</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0052</v>
+        <v>-1.2104</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0825</v>
+        <v>1.8529</v>
       </c>
       <c r="G7" t="n">
-        <v>1.889</v>
+        <v>2.1658</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8267</v>
+        <v>-1.019</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0623</v>
+        <v>3.1849</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1832</v>
+        <v>0.2933</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5414</v>
+        <v>-1.0441</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6418</v>
+        <v>1.3374</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2942</v>
+        <v>1.8726</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7147</v>
+        <v>0.0251</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4205</v>
+        <v>1.8475</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.6005</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.0009</v>
+        <v>-2.1421</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4004</v>
+        <v>1.5579</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0912</v>
+        <v>-0.8359</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9669</v>
+        <v>0.1311</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8756</v>
+        <v>-0.967</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.12</v>
+        <v>-0.1032</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7794</v>
+        <v>0.5074</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8993</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. GOMEZ GARCIA</t>
+          <t>S. YURCHENKO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0756</v>
+        <v>0.4911</v>
       </c>
       <c r="E8" t="n">
-        <v>0.097</v>
+        <v>-0.0635</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0214</v>
+        <v>0.5545</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3032</v>
+        <v>1.8882</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4617</v>
+        <v>0.8298</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7648</v>
+        <v>1.0584</v>
       </c>
       <c r="J8" t="n">
-        <v>0.14</v>
+        <v>2.2868</v>
       </c>
       <c r="K8" t="n">
-        <v>0.06</v>
+        <v>1.6139</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1632</v>
+        <v>-0.3986</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.7842</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6849</v>
+        <v>0.3856</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2001</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0003</v>
+        <v>-2.921</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2003</v>
+        <v>1.3632</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5675</v>
+        <v>0.2829</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5023</v>
+        <v>-0.2676</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.5505</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1398</v>
+        <v>-0.1221</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4596</v>
+        <v>0.8384</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3197</v>
+        <v>-0.9605</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5468</v>
+        <v>-1.3893</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9473</v>
+        <v>-1.6344</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4005</v>
+        <v>0.245</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5465</v>
+        <v>-1.564</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.5347</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0379</v>
+        <v>-1.0292</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.296</v>
+        <v>-1.268</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.316</v>
+        <v>-1.2885</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2505</v>
+        <v>-0.296</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5286</v>
+        <v>-0.5553</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2781</v>
+        <v>0.2592</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0002</v>
+        <v>0.1747</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4512</v>
+        <v>-0.1717</v>
       </c>
       <c r="U9" t="n">
-        <v>0.451</v>
+        <v>0.3463</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. GADEA HIERRO</t>
+          <t>M. TORTAROLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0988</v>
+        <v>-1.7114</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7506</v>
+        <v>-3.0955</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3483</v>
+        <v>1.3841</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5598</v>
+        <v>0.31</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9889</v>
+        <v>-1.0274</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4291</v>
+        <v>1.3374</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3504</v>
+        <v>-0.6744</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9522</v>
+        <v>-0.5695</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6018</v>
+        <v>-0.1049</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7906</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0367</v>
+        <v>-0.4578</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8273</v>
+        <v>1.4422</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.2003</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.4007</v>
+        <v>-3.1158</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2003</v>
+        <v>1.7526</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4009</v>
+        <v>-0.6583</v>
       </c>
       <c r="T10" t="n">
-        <v>2.0808</v>
+        <v>0.1357</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3201</v>
+        <v>-0.794</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.7396</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0803</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.6593</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. TORTAROLO</t>
+          <t>A. GADEA HIERRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.25</v>
+        <v>-3.8108</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5653</v>
+        <v>-3.0093</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3153</v>
+        <v>-0.8016</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3314</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-1.9977</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3198</v>
+        <v>1.4166</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8086</v>
+        <v>-1.2457</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6162</v>
+        <v>-1.878</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1924</v>
+        <v>0.6323</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1399</v>
+        <v>0.6646</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3722</v>
+        <v>-0.1197</v>
       </c>
       <c r="O11" t="n">
-        <v>1.5122</v>
+        <v>0.7843</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.4004</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.2009</v>
+        <v>-2.3368</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8005</v>
+        <v>1.1684</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.181</v>
+        <v>0.7118</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.6248</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1056</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-2.7732</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5196</v>
+        <v>-0.0516</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5196</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.751299999999999</v>
+        <v>3.321900000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-12.8252</v>
+        <v>-9.0578</v>
       </c>
       <c r="F12" t="n">
-        <v>14.5762</v>
+        <v>12.3793</v>
       </c>
       <c r="G12" t="n">
-        <v>12.4921</v>
+        <v>12.303</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2870999999999995</v>
+        <v>-0.4208999999999996</v>
       </c>
       <c r="I12" t="n">
-        <v>12.7792</v>
+        <v>12.7241</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5863</v>
+        <v>3.604099999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>1.4704</v>
+        <v>2.045599999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>1.115900000000001</v>
+        <v>1.5586</v>
       </c>
       <c r="M12" t="n">
-        <v>9.9056</v>
+        <v>8.6989</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.7575</v>
+        <v>-2.4666</v>
       </c>
       <c r="O12" t="n">
-        <v>11.6633</v>
+        <v>11.1652</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.0014</v>
+        <v>-4.8685</v>
       </c>
       <c r="Q12" t="n">
-        <v>-21.0061</v>
+        <v>-20.4472</v>
       </c>
       <c r="R12" t="n">
-        <v>16.0046</v>
+        <v>15.5788</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.7792</v>
+        <v>-2.1781</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.8213</v>
+        <v>-0.01819999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.9578</v>
+        <v>-2.1597</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.9603</v>
+        <v>-1.9348</v>
       </c>
       <c r="W12" t="n">
-        <v>7.416099999999999</v>
+        <v>7.803700000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.376100000000001</v>
+        <v>-9.7386</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4178</v>
+        <v>4.8455</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8681</v>
+        <v>2.7774</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5496</v>
+        <v>2.0681</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2486</v>
+        <v>-0.2747</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.0397</v>
+        <v>-1.0674</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7911</v>
+        <v>0.7926</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6456</v>
+        <v>0.7239</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.196</v>
+        <v>-1.1648</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8416</v>
+        <v>1.8887</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8942</v>
+        <v>-0.9986</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1563</v>
+        <v>0.0974</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0505</v>
+        <v>-1.096</v>
       </c>
       <c r="P13" t="n">
-        <v>2.8008</v>
+        <v>2.7263</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R13" t="n">
-        <v>3.0009</v>
+        <v>2.921</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0975</v>
+        <v>1.6303</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2228</v>
+        <v>1.0272</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8747</v>
+        <v>0.6031</v>
       </c>
       <c r="V13" t="n">
-        <v>0.768</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.4317</v>
+        <v>-0.4575</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4928</v>
+        <v>2.7903</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4134</v>
+        <v>1.3186</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0795</v>
+        <v>1.4717</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1043</v>
+        <v>-0.1171</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1581</v>
+        <v>0.1308</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2624</v>
+        <v>-0.2479</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2744</v>
+        <v>-0.1961</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4017</v>
+        <v>0.4439</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6761</v>
+        <v>-0.6401</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1701</v>
+        <v>0.079</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2435</v>
+        <v>-0.3131</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4137</v>
+        <v>0.3921</v>
       </c>
       <c r="P14" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3226</v>
+        <v>-0.0411</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4311</v>
+        <v>0.2926</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8914</v>
+        <v>-0.3336</v>
       </c>
       <c r="V14" t="n">
-        <v>1.7194</v>
+        <v>1.78</v>
       </c>
       <c r="W14" t="n">
-        <v>2.3192</v>
+        <v>2.3905</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3849</v>
+        <v>1.7005</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.886</v>
+        <v>-0.7486</v>
       </c>
       <c r="F15" t="n">
-        <v>2.271</v>
+        <v>2.4491</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0041</v>
+        <v>0.1362</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8279</v>
+        <v>2.9158</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.832</v>
+        <v>-2.7796</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6453</v>
+        <v>-0.4192</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7428</v>
+        <v>2.8789</v>
       </c>
       <c r="L15" t="n">
-        <v>-3.3881</v>
+        <v>-3.2981</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6412</v>
+        <v>0.5554</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0851</v>
+        <v>0.0369</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5561</v>
+        <v>0.5185</v>
       </c>
       <c r="P15" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1492</v>
+        <v>0.3043</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6603</v>
+        <v>0.4679</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5111</v>
+        <v>-0.1636</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1606</v>
+        <v>-0.1032</v>
       </c>
       <c r="W15" t="n">
-        <v>0.0992</v>
+        <v>0.1763</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MARTIN FERNANDEZ</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1926</v>
+        <v>1.202</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3971</v>
+        <v>-1.224</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7955</v>
+        <v>2.426</v>
       </c>
       <c r="G16" t="n">
-        <v>0.318</v>
+        <v>-1.1134</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2643</v>
+        <v>-1.4132</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0537</v>
+        <v>0.2998</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3617</v>
+        <v>-1.5912</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3217</v>
+        <v>-0.9671999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>0.04</v>
+        <v>-0.624</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0437</v>
+        <v>0.4777</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0574</v>
+        <v>-0.446</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0137</v>
+        <v>0.9237</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2001</v>
+        <v>1.3632</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0003</v>
+        <v>-0.1947</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2003</v>
+        <v>1.5579</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1941</v>
+        <v>0.4682</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7759</v>
+        <v>0.2824</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4182</v>
+        <v>0.1857</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5196</v>
+        <v>0.4841</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.7794</v>
+        <v>0.2046</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>H. MARTORELL TRONCHONI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9367</v>
+        <v>0.9859</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1456</v>
+        <v>1.0431</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0823</v>
+        <v>-0.0572</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0954</v>
+        <v>0.9263</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4134</v>
+        <v>1.1582</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3181</v>
+        <v>-0.2318</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.6723</v>
+        <v>1.0053</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.0343</v>
+        <v>0.9647</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.638</v>
+        <v>0.0405</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5769</v>
+        <v>-0.0789</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3791</v>
+        <v>0.1934</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9560999999999999</v>
+        <v>-0.2724</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4004</v>
+        <v>0.1947</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2001</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6005</v>
+        <v>0.1947</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1234</v>
+        <v>-0.1352</v>
       </c>
       <c r="T17" t="n">
-        <v>0.467</v>
+        <v>0.0378</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3435</v>
+        <v>-0.1731</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5083</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2598</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.2485</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H. MARTORELL TRONCHONI</t>
+          <t>J. MARTIN FERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8253</v>
+        <v>0.3303</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9153</v>
+        <v>-0.3168</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.09</v>
+        <v>0.6471</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9222</v>
+        <v>0.305</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1466</v>
+        <v>0.2776</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2243</v>
+        <v>0.0274</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9797</v>
+        <v>0.4023</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9397</v>
+        <v>0.3618</v>
       </c>
       <c r="L18" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0575</v>
+        <v>-0.0973</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2069</v>
+        <v>-0.0842</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2643</v>
+        <v>-0.0131</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2001</v>
+        <v>1.1684</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.297</v>
+        <v>0.3895</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0645</v>
+        <v>-0.0249</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2325</v>
+        <v>0.4144</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.8384</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BOSCH ROIG</t>
+          <t>M. MARTINEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1896</v>
+        <v>-1.1271</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1193</v>
+        <v>-2.2692</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9297</v>
+        <v>1.1421</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.0695</v>
+        <v>-1.1572</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3225</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.747</v>
+        <v>-1.248</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.9683</v>
+        <v>-0.3455</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3363</v>
+        <v>0.4644</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.632</v>
+        <v>-0.8099</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1012</v>
+        <v>-0.8117</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0138</v>
+        <v>-0.3736</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.115</v>
+        <v>-0.4381</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0003</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2001</v>
+        <v>-3.3105</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2003</v>
+        <v>2.7263</v>
       </c>
       <c r="S19" t="n">
-        <v>1.8196</v>
+        <v>0.4612</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7893</v>
+        <v>-0.4448</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0303</v>
+        <v>0.9061</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.1531</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2598</v>
+        <v>1.8316</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1998</v>
+        <v>-1.6785</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ZURBRIGGEN</t>
+          <t>J. BOSCH ROIG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1203</v>
+        <v>-1.27</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.2031</v>
+        <v>-2.0831</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0828</v>
+        <v>0.8131</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.9862</v>
+        <v>-3.0354</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7416</v>
+        <v>-0.3058</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2446</v>
+        <v>-2.7296</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.5702</v>
+        <v>-2.8591</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1018</v>
+        <v>-0.2822</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.672</v>
+        <v>-2.577</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.416</v>
+        <v>-0.1762</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8434</v>
+        <v>-0.0236</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4274</v>
+        <v>-0.1526</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2001</v>
+        <v>0.9737</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.4007</v>
+        <v>-0.1947</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2006</v>
+        <v>1.1684</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5617</v>
+        <v>1.7332</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2113</v>
+        <v>0.6913</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6496</v>
+        <v>1.042</v>
       </c>
       <c r="V20" t="n">
-        <v>1.6277</v>
+        <v>-0.9416</v>
       </c>
       <c r="W20" t="n">
-        <v>1.9791</v>
+        <v>0.2795</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3514</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. PELUFO LOZANO</t>
+          <t>A. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3915</v>
+        <v>-1.6189</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1579</v>
+        <v>-3.5165</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7663</v>
+        <v>1.8977</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4025</v>
+        <v>-3.0313</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.75</v>
+        <v>-0.7929</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6525</v>
+        <v>-2.2385</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6508</v>
+        <v>-2.4815</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7707000000000001</v>
+        <v>0.136</v>
       </c>
       <c r="L21" t="n">
-        <v>0.12</v>
+        <v>-2.6175</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7517</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0207</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7725</v>
+        <v>0.379</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.4004</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.2012</v>
+        <v>-2.3368</v>
       </c>
       <c r="R21" t="n">
-        <v>2.8008</v>
+        <v>2.1421</v>
       </c>
       <c r="S21" t="n">
-        <v>2.1307</v>
+        <v>-0.0464</v>
       </c>
       <c r="T21" t="n">
-        <v>1.6941</v>
+        <v>-0.7577</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4366</v>
+        <v>0.7113</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.7194</v>
+        <v>1.6536</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.0595</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7194</v>
+        <v>-0.4059</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. MARTINEZ HERNANDEZ</t>
+          <t>V. PELUFO LOZANO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6399</v>
+        <v>-3.3444</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4947</v>
+        <v>-3.8114</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8548</v>
+        <v>0.467</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1691</v>
+        <v>-1.3842</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1069</v>
+        <v>-0.669</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.276</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4887</v>
+        <v>-0.512</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4217</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.9104</v>
+        <v>0.1216</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6805</v>
+        <v>-0.8722</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3148</v>
+        <v>-0.0355</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3657</v>
+        <v>-0.8368</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6002</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.401</v>
+        <v>-4.0895</v>
       </c>
       <c r="R22" t="n">
-        <v>2.8008</v>
+        <v>2.7263</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0387</v>
+        <v>1.183</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4047</v>
+        <v>0.79</v>
       </c>
       <c r="U22" t="n">
-        <v>0.366</v>
+        <v>0.3929</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1682</v>
+        <v>-1.78</v>
       </c>
       <c r="W22" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.6315</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.66</v>
+        <v>-3.6119</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1637</v>
+        <v>-3.549</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4964</v>
+        <v>-0.063</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.6526</v>
+        <v>-3.5573</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0505</v>
+        <v>0.096</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.7031</v>
+        <v>-3.6533</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.6228</v>
+        <v>-2.4258</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1654</v>
+        <v>0.2644</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.7882</v>
+        <v>-2.6902</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0298</v>
+        <v>-1.1315</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1149</v>
+        <v>-0.1684</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9149</v>
+        <v>-0.9631</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5154</v>
+        <v>0.4349</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.54</v>
+        <v>-0.2021</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0246</v>
+        <v>0.637</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5083</v>
+        <v>0.4841</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6915</v>
+        <v>-0.737</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.751200000000002</v>
+        <v>0.8821999999999997</v>
       </c>
       <c r="E24" t="n">
-        <v>-14.5764</v>
+        <v>-12.3795</v>
       </c>
       <c r="F24" t="n">
-        <v>12.8251</v>
+        <v>13.2617</v>
       </c>
       <c r="G24" t="n">
-        <v>-12.4921</v>
+        <v>-12.3031</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2870999999999999</v>
+        <v>0.4208999999999998</v>
       </c>
       <c r="I24" t="n">
-        <v>-12.779</v>
+        <v>-12.7241</v>
       </c>
       <c r="J24" t="n">
-        <v>-9.905799999999999</v>
+        <v>-8.6989</v>
       </c>
       <c r="K24" t="n">
-        <v>1.7575</v>
+        <v>2.4663</v>
       </c>
       <c r="L24" t="n">
-        <v>-11.6632</v>
+        <v>-11.1655</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.5864</v>
+        <v>-3.6042</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4703</v>
+        <v>-2.0456</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.1159</v>
+        <v>-1.5588</v>
       </c>
       <c r="P24" t="n">
-        <v>5.001399999999999</v>
+        <v>4.8684</v>
       </c>
       <c r="Q24" t="n">
-        <v>-16.0047</v>
+        <v>-15.5788</v>
       </c>
       <c r="R24" t="n">
-        <v>21.006</v>
+        <v>20.4471</v>
       </c>
       <c r="S24" t="n">
-        <v>3.779099999999999</v>
+        <v>6.381899999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>1.9578</v>
+        <v>2.1597</v>
       </c>
       <c r="U24" t="n">
-        <v>1.8215</v>
+        <v>4.2222</v>
       </c>
       <c r="V24" t="n">
-        <v>1.9603</v>
+        <v>1.9347</v>
       </c>
       <c r="W24" t="n">
-        <v>9.376199999999999</v>
+        <v>9.7386</v>
       </c>
       <c r="X24" t="n">
-        <v>-7.415900000000001</v>
+        <v>-7.803800000000001</v>
       </c>
     </row>
   </sheetData>
